--- a/Knowledge/Model Outputs/PG/PG_model.xlsx
+++ b/Knowledge/Model Outputs/PG/PG_model.xlsx
@@ -6130,87 +6130,87 @@
         <v/>
       </c>
       <c r="V2" s="14">
-        <f>T2</f>
+        <f>U2</f>
         <v/>
       </c>
       <c r="W2" s="14">
-        <f>T2</f>
+        <f>V2</f>
         <v/>
       </c>
       <c r="X2" s="14">
-        <f>T2</f>
+        <f>W2</f>
         <v/>
       </c>
       <c r="Y2" s="14">
-        <f>T2</f>
+        <f>X2</f>
         <v/>
       </c>
       <c r="Z2" s="14">
-        <f>T2</f>
+        <f>Y2</f>
         <v/>
       </c>
       <c r="AA2" s="14">
-        <f>T2</f>
+        <f>Z2</f>
         <v/>
       </c>
       <c r="AB2" s="14">
-        <f>T2</f>
+        <f>AA2</f>
         <v/>
       </c>
       <c r="AC2" s="14">
-        <f>T2</f>
+        <f>AB2</f>
         <v/>
       </c>
       <c r="AD2" s="14">
-        <f>T2</f>
+        <f>AC2</f>
         <v/>
       </c>
       <c r="AE2" s="14">
-        <f>T2</f>
+        <f>AD2</f>
         <v/>
       </c>
       <c r="AF2" s="14">
-        <f>T2</f>
+        <f>AE2</f>
         <v/>
       </c>
       <c r="AG2" s="14">
-        <f>T2</f>
+        <f>AF2</f>
         <v/>
       </c>
       <c r="AH2" s="14">
-        <f>T2</f>
+        <f>AG2</f>
         <v/>
       </c>
       <c r="AI2" s="14">
-        <f>T2</f>
+        <f>AH2</f>
         <v/>
       </c>
       <c r="AJ2" s="14">
-        <f>T2</f>
+        <f>AI2</f>
         <v/>
       </c>
       <c r="AK2" s="14">
-        <f>T2</f>
+        <f>AJ2</f>
         <v/>
       </c>
       <c r="AL2" s="14">
-        <f>T2</f>
+        <f>AK2</f>
         <v/>
       </c>
       <c r="AM2" s="14">
-        <f>T2</f>
+        <f>AL2</f>
         <v/>
       </c>
       <c r="AN2" s="14">
-        <f>T2</f>
+        <f>AM2</f>
         <v/>
       </c>
       <c r="AO2" s="14">
-        <f>T2</f>
+        <f>AN2</f>
         <v/>
       </c>
       <c r="AP2" s="14">
-        <f>T2</f>
+        <f>AO2</f>
         <v/>
       </c>
     </row>
@@ -6297,87 +6297,87 @@
         <v/>
       </c>
       <c r="V3" s="14">
-        <f>T3</f>
+        <f>U3</f>
         <v/>
       </c>
       <c r="W3" s="14">
-        <f>T3</f>
+        <f>V3</f>
         <v/>
       </c>
       <c r="X3" s="14">
-        <f>T3</f>
+        <f>W3</f>
         <v/>
       </c>
       <c r="Y3" s="14">
-        <f>T3</f>
+        <f>X3</f>
         <v/>
       </c>
       <c r="Z3" s="14">
-        <f>T3</f>
+        <f>Y3</f>
         <v/>
       </c>
       <c r="AA3" s="14">
-        <f>T3</f>
+        <f>Z3</f>
         <v/>
       </c>
       <c r="AB3" s="14">
-        <f>T3</f>
+        <f>AA3</f>
         <v/>
       </c>
       <c r="AC3" s="14">
-        <f>T3</f>
+        <f>AB3</f>
         <v/>
       </c>
       <c r="AD3" s="14">
-        <f>T3</f>
+        <f>AC3</f>
         <v/>
       </c>
       <c r="AE3" s="14">
-        <f>T3</f>
+        <f>AD3</f>
         <v/>
       </c>
       <c r="AF3" s="14">
-        <f>T3</f>
+        <f>AE3</f>
         <v/>
       </c>
       <c r="AG3" s="14">
-        <f>T3</f>
+        <f>AF3</f>
         <v/>
       </c>
       <c r="AH3" s="14">
-        <f>T3</f>
+        <f>AG3</f>
         <v/>
       </c>
       <c r="AI3" s="14">
-        <f>T3</f>
+        <f>AH3</f>
         <v/>
       </c>
       <c r="AJ3" s="14">
-        <f>T3</f>
+        <f>AI3</f>
         <v/>
       </c>
       <c r="AK3" s="14">
-        <f>T3</f>
+        <f>AJ3</f>
         <v/>
       </c>
       <c r="AL3" s="14">
-        <f>T3</f>
+        <f>AK3</f>
         <v/>
       </c>
       <c r="AM3" s="14">
-        <f>T3</f>
+        <f>AL3</f>
         <v/>
       </c>
       <c r="AN3" s="14">
-        <f>T3</f>
+        <f>AM3</f>
         <v/>
       </c>
       <c r="AO3" s="14">
-        <f>T3</f>
+        <f>AN3</f>
         <v/>
       </c>
       <c r="AP3" s="14">
-        <f>T3</f>
+        <f>AO3</f>
         <v/>
       </c>
     </row>
@@ -6464,87 +6464,87 @@
         <v/>
       </c>
       <c r="V4" s="14">
-        <f>T4</f>
+        <f>U4</f>
         <v/>
       </c>
       <c r="W4" s="14">
-        <f>T4</f>
+        <f>V4</f>
         <v/>
       </c>
       <c r="X4" s="14">
-        <f>T4</f>
+        <f>W4</f>
         <v/>
       </c>
       <c r="Y4" s="14">
-        <f>T4</f>
+        <f>X4</f>
         <v/>
       </c>
       <c r="Z4" s="14">
-        <f>T4</f>
+        <f>Y4</f>
         <v/>
       </c>
       <c r="AA4" s="14">
-        <f>T4</f>
+        <f>Z4</f>
         <v/>
       </c>
       <c r="AB4" s="14">
-        <f>T4</f>
+        <f>AA4</f>
         <v/>
       </c>
       <c r="AC4" s="14">
-        <f>T4</f>
+        <f>AB4</f>
         <v/>
       </c>
       <c r="AD4" s="14">
-        <f>T4</f>
+        <f>AC4</f>
         <v/>
       </c>
       <c r="AE4" s="14">
-        <f>T4</f>
+        <f>AD4</f>
         <v/>
       </c>
       <c r="AF4" s="14">
-        <f>T4</f>
+        <f>AE4</f>
         <v/>
       </c>
       <c r="AG4" s="14">
-        <f>T4</f>
+        <f>AF4</f>
         <v/>
       </c>
       <c r="AH4" s="14">
-        <f>T4</f>
+        <f>AG4</f>
         <v/>
       </c>
       <c r="AI4" s="14">
-        <f>T4</f>
+        <f>AH4</f>
         <v/>
       </c>
       <c r="AJ4" s="14">
-        <f>T4</f>
+        <f>AI4</f>
         <v/>
       </c>
       <c r="AK4" s="14">
-        <f>T4</f>
+        <f>AJ4</f>
         <v/>
       </c>
       <c r="AL4" s="14">
-        <f>T4</f>
+        <f>AK4</f>
         <v/>
       </c>
       <c r="AM4" s="14">
-        <f>T4</f>
+        <f>AL4</f>
         <v/>
       </c>
       <c r="AN4" s="14">
-        <f>T4</f>
+        <f>AM4</f>
         <v/>
       </c>
       <c r="AO4" s="14">
-        <f>T4</f>
+        <f>AN4</f>
         <v/>
       </c>
       <c r="AP4" s="14">
-        <f>T4</f>
+        <f>AO4</f>
         <v/>
       </c>
     </row>
@@ -6631,87 +6631,87 @@
         <v/>
       </c>
       <c r="V5" s="14">
-        <f>T5</f>
+        <f>U5</f>
         <v/>
       </c>
       <c r="W5" s="14">
-        <f>T5</f>
+        <f>V5</f>
         <v/>
       </c>
       <c r="X5" s="14">
-        <f>T5</f>
+        <f>W5</f>
         <v/>
       </c>
       <c r="Y5" s="14">
-        <f>T5</f>
+        <f>X5</f>
         <v/>
       </c>
       <c r="Z5" s="14">
-        <f>T5</f>
+        <f>Y5</f>
         <v/>
       </c>
       <c r="AA5" s="14">
-        <f>T5</f>
+        <f>Z5</f>
         <v/>
       </c>
       <c r="AB5" s="14">
-        <f>T5</f>
+        <f>AA5</f>
         <v/>
       </c>
       <c r="AC5" s="14">
-        <f>T5</f>
+        <f>AB5</f>
         <v/>
       </c>
       <c r="AD5" s="14">
-        <f>T5</f>
+        <f>AC5</f>
         <v/>
       </c>
       <c r="AE5" s="14">
-        <f>T5</f>
+        <f>AD5</f>
         <v/>
       </c>
       <c r="AF5" s="14">
-        <f>T5</f>
+        <f>AE5</f>
         <v/>
       </c>
       <c r="AG5" s="14">
-        <f>T5</f>
+        <f>AF5</f>
         <v/>
       </c>
       <c r="AH5" s="14">
-        <f>T5</f>
+        <f>AG5</f>
         <v/>
       </c>
       <c r="AI5" s="14">
-        <f>T5</f>
+        <f>AH5</f>
         <v/>
       </c>
       <c r="AJ5" s="14">
-        <f>T5</f>
+        <f>AI5</f>
         <v/>
       </c>
       <c r="AK5" s="14">
-        <f>T5</f>
+        <f>AJ5</f>
         <v/>
       </c>
       <c r="AL5" s="14">
-        <f>T5</f>
+        <f>AK5</f>
         <v/>
       </c>
       <c r="AM5" s="14">
-        <f>T5</f>
+        <f>AL5</f>
         <v/>
       </c>
       <c r="AN5" s="14">
-        <f>T5</f>
+        <f>AM5</f>
         <v/>
       </c>
       <c r="AO5" s="14">
-        <f>T5</f>
+        <f>AN5</f>
         <v/>
       </c>
       <c r="AP5" s="14">
-        <f>T5</f>
+        <f>AO5</f>
         <v/>
       </c>
     </row>
@@ -6798,87 +6798,87 @@
         <v/>
       </c>
       <c r="V6" s="15">
-        <f>T6</f>
+        <f>U6</f>
         <v/>
       </c>
       <c r="W6" s="15">
-        <f>T6</f>
+        <f>V6</f>
         <v/>
       </c>
       <c r="X6" s="15">
-        <f>T6</f>
+        <f>W6</f>
         <v/>
       </c>
       <c r="Y6" s="15">
-        <f>T6</f>
+        <f>X6</f>
         <v/>
       </c>
       <c r="Z6" s="15">
-        <f>T6</f>
+        <f>Y6</f>
         <v/>
       </c>
       <c r="AA6" s="15">
-        <f>T6</f>
+        <f>Z6</f>
         <v/>
       </c>
       <c r="AB6" s="15">
-        <f>T6</f>
+        <f>AA6</f>
         <v/>
       </c>
       <c r="AC6" s="15">
-        <f>T6</f>
+        <f>AB6</f>
         <v/>
       </c>
       <c r="AD6" s="15">
-        <f>T6</f>
+        <f>AC6</f>
         <v/>
       </c>
       <c r="AE6" s="15">
-        <f>T6</f>
+        <f>AD6</f>
         <v/>
       </c>
       <c r="AF6" s="15">
-        <f>T6</f>
+        <f>AE6</f>
         <v/>
       </c>
       <c r="AG6" s="15">
-        <f>T6</f>
+        <f>AF6</f>
         <v/>
       </c>
       <c r="AH6" s="15">
-        <f>T6</f>
+        <f>AG6</f>
         <v/>
       </c>
       <c r="AI6" s="15">
-        <f>T6</f>
+        <f>AH6</f>
         <v/>
       </c>
       <c r="AJ6" s="15">
-        <f>T6</f>
+        <f>AI6</f>
         <v/>
       </c>
       <c r="AK6" s="15">
-        <f>T6</f>
+        <f>AJ6</f>
         <v/>
       </c>
       <c r="AL6" s="15">
-        <f>T6</f>
+        <f>AK6</f>
         <v/>
       </c>
       <c r="AM6" s="15">
-        <f>T6</f>
+        <f>AL6</f>
         <v/>
       </c>
       <c r="AN6" s="15">
-        <f>T6</f>
+        <f>AM6</f>
         <v/>
       </c>
       <c r="AO6" s="15">
-        <f>T6</f>
+        <f>AN6</f>
         <v/>
       </c>
       <c r="AP6" s="15">
-        <f>T6</f>
+        <f>AO6</f>
         <v/>
       </c>
     </row>
@@ -6965,87 +6965,87 @@
         <v/>
       </c>
       <c r="V7" s="15">
-        <f>T7</f>
+        <f>U7</f>
         <v/>
       </c>
       <c r="W7" s="15">
-        <f>T7</f>
+        <f>V7</f>
         <v/>
       </c>
       <c r="X7" s="15">
-        <f>T7</f>
+        <f>W7</f>
         <v/>
       </c>
       <c r="Y7" s="15">
-        <f>T7</f>
+        <f>X7</f>
         <v/>
       </c>
       <c r="Z7" s="15">
-        <f>T7</f>
+        <f>Y7</f>
         <v/>
       </c>
       <c r="AA7" s="15">
-        <f>T7</f>
+        <f>Z7</f>
         <v/>
       </c>
       <c r="AB7" s="15">
-        <f>T7</f>
+        <f>AA7</f>
         <v/>
       </c>
       <c r="AC7" s="15">
-        <f>T7</f>
+        <f>AB7</f>
         <v/>
       </c>
       <c r="AD7" s="15">
-        <f>T7</f>
+        <f>AC7</f>
         <v/>
       </c>
       <c r="AE7" s="15">
-        <f>T7</f>
+        <f>AD7</f>
         <v/>
       </c>
       <c r="AF7" s="15">
-        <f>T7</f>
+        <f>AE7</f>
         <v/>
       </c>
       <c r="AG7" s="15">
-        <f>T7</f>
+        <f>AF7</f>
         <v/>
       </c>
       <c r="AH7" s="15">
-        <f>T7</f>
+        <f>AG7</f>
         <v/>
       </c>
       <c r="AI7" s="15">
-        <f>T7</f>
+        <f>AH7</f>
         <v/>
       </c>
       <c r="AJ7" s="15">
-        <f>T7</f>
+        <f>AI7</f>
         <v/>
       </c>
       <c r="AK7" s="15">
-        <f>T7</f>
+        <f>AJ7</f>
         <v/>
       </c>
       <c r="AL7" s="15">
-        <f>T7</f>
+        <f>AK7</f>
         <v/>
       </c>
       <c r="AM7" s="15">
-        <f>T7</f>
+        <f>AL7</f>
         <v/>
       </c>
       <c r="AN7" s="15">
-        <f>T7</f>
+        <f>AM7</f>
         <v/>
       </c>
       <c r="AO7" s="15">
-        <f>T7</f>
+        <f>AN7</f>
         <v/>
       </c>
       <c r="AP7" s="15">
-        <f>T7</f>
+        <f>AO7</f>
         <v/>
       </c>
     </row>
@@ -7132,87 +7132,87 @@
         <v/>
       </c>
       <c r="V8" s="14">
-        <f>T8</f>
+        <f>U8</f>
         <v/>
       </c>
       <c r="W8" s="14">
-        <f>T8</f>
+        <f>V8</f>
         <v/>
       </c>
       <c r="X8" s="14">
-        <f>T8</f>
+        <f>W8</f>
         <v/>
       </c>
       <c r="Y8" s="14">
-        <f>T8</f>
+        <f>X8</f>
         <v/>
       </c>
       <c r="Z8" s="14">
-        <f>T8</f>
+        <f>Y8</f>
         <v/>
       </c>
       <c r="AA8" s="14">
-        <f>T8</f>
+        <f>Z8</f>
         <v/>
       </c>
       <c r="AB8" s="14">
-        <f>T8</f>
+        <f>AA8</f>
         <v/>
       </c>
       <c r="AC8" s="14">
-        <f>T8</f>
+        <f>AB8</f>
         <v/>
       </c>
       <c r="AD8" s="14">
-        <f>T8</f>
+        <f>AC8</f>
         <v/>
       </c>
       <c r="AE8" s="14">
-        <f>T8</f>
+        <f>AD8</f>
         <v/>
       </c>
       <c r="AF8" s="14">
-        <f>T8</f>
+        <f>AE8</f>
         <v/>
       </c>
       <c r="AG8" s="14">
-        <f>T8</f>
+        <f>AF8</f>
         <v/>
       </c>
       <c r="AH8" s="14">
-        <f>T8</f>
+        <f>AG8</f>
         <v/>
       </c>
       <c r="AI8" s="14">
-        <f>T8</f>
+        <f>AH8</f>
         <v/>
       </c>
       <c r="AJ8" s="14">
-        <f>T8</f>
+        <f>AI8</f>
         <v/>
       </c>
       <c r="AK8" s="14">
-        <f>T8</f>
+        <f>AJ8</f>
         <v/>
       </c>
       <c r="AL8" s="14">
-        <f>T8</f>
+        <f>AK8</f>
         <v/>
       </c>
       <c r="AM8" s="14">
-        <f>T8</f>
+        <f>AL8</f>
         <v/>
       </c>
       <c r="AN8" s="14">
-        <f>T8</f>
+        <f>AM8</f>
         <v/>
       </c>
       <c r="AO8" s="14">
-        <f>T8</f>
+        <f>AN8</f>
         <v/>
       </c>
       <c r="AP8" s="14">
-        <f>T8</f>
+        <f>AO8</f>
         <v/>
       </c>
     </row>
@@ -7299,87 +7299,87 @@
         <v/>
       </c>
       <c r="V9" s="15">
-        <f>T9</f>
+        <f>U9</f>
         <v/>
       </c>
       <c r="W9" s="15">
-        <f>T9</f>
+        <f>V9</f>
         <v/>
       </c>
       <c r="X9" s="15">
-        <f>T9</f>
+        <f>W9</f>
         <v/>
       </c>
       <c r="Y9" s="15">
-        <f>T9</f>
+        <f>X9</f>
         <v/>
       </c>
       <c r="Z9" s="15">
-        <f>T9</f>
+        <f>Y9</f>
         <v/>
       </c>
       <c r="AA9" s="15">
-        <f>T9</f>
+        <f>Z9</f>
         <v/>
       </c>
       <c r="AB9" s="15">
-        <f>T9</f>
+        <f>AA9</f>
         <v/>
       </c>
       <c r="AC9" s="15">
-        <f>T9</f>
+        <f>AB9</f>
         <v/>
       </c>
       <c r="AD9" s="15">
-        <f>T9</f>
+        <f>AC9</f>
         <v/>
       </c>
       <c r="AE9" s="15">
-        <f>T9</f>
+        <f>AD9</f>
         <v/>
       </c>
       <c r="AF9" s="15">
-        <f>T9</f>
+        <f>AE9</f>
         <v/>
       </c>
       <c r="AG9" s="15">
-        <f>T9</f>
+        <f>AF9</f>
         <v/>
       </c>
       <c r="AH9" s="15">
-        <f>T9</f>
+        <f>AG9</f>
         <v/>
       </c>
       <c r="AI9" s="15">
-        <f>T9</f>
+        <f>AH9</f>
         <v/>
       </c>
       <c r="AJ9" s="15">
-        <f>T9</f>
+        <f>AI9</f>
         <v/>
       </c>
       <c r="AK9" s="15">
-        <f>T9</f>
+        <f>AJ9</f>
         <v/>
       </c>
       <c r="AL9" s="15">
-        <f>T9</f>
+        <f>AK9</f>
         <v/>
       </c>
       <c r="AM9" s="15">
-        <f>T9</f>
+        <f>AL9</f>
         <v/>
       </c>
       <c r="AN9" s="15">
-        <f>T9</f>
+        <f>AM9</f>
         <v/>
       </c>
       <c r="AO9" s="15">
-        <f>T9</f>
+        <f>AN9</f>
         <v/>
       </c>
       <c r="AP9" s="15">
-        <f>T9</f>
+        <f>AO9</f>
         <v/>
       </c>
     </row>
@@ -7860,87 +7860,87 @@
         <v/>
       </c>
       <c r="R3" s="17">
-        <f>P3</f>
+        <f>Q3</f>
         <v/>
       </c>
       <c r="S3" s="17">
-        <f>P3</f>
+        <f>R3</f>
         <v/>
       </c>
       <c r="T3" s="17">
-        <f>P3</f>
+        <f>S3</f>
         <v/>
       </c>
       <c r="U3" s="17">
-        <f>P3</f>
+        <f>T3</f>
         <v/>
       </c>
       <c r="V3" s="17">
-        <f>P3</f>
+        <f>U3</f>
         <v/>
       </c>
       <c r="W3" s="17">
-        <f>P3</f>
+        <f>V3</f>
         <v/>
       </c>
       <c r="X3" s="17">
-        <f>P3</f>
+        <f>W3</f>
         <v/>
       </c>
       <c r="Y3" s="17">
-        <f>P3</f>
+        <f>X3</f>
         <v/>
       </c>
       <c r="Z3" s="17">
-        <f>P3</f>
+        <f>Y3</f>
         <v/>
       </c>
       <c r="AA3" s="17">
-        <f>P3</f>
+        <f>Z3</f>
         <v/>
       </c>
       <c r="AB3" s="17">
-        <f>P3</f>
+        <f>AA3</f>
         <v/>
       </c>
       <c r="AC3" s="17">
-        <f>P3</f>
+        <f>AB3</f>
         <v/>
       </c>
       <c r="AD3" s="17">
-        <f>P3</f>
+        <f>AC3</f>
         <v/>
       </c>
       <c r="AE3" s="17">
-        <f>P3</f>
+        <f>AD3</f>
         <v/>
       </c>
       <c r="AF3" s="17">
-        <f>P3</f>
+        <f>AE3</f>
         <v/>
       </c>
       <c r="AG3" s="17">
-        <f>P3</f>
+        <f>AF3</f>
         <v/>
       </c>
       <c r="AH3" s="17">
-        <f>P3</f>
+        <f>AG3</f>
         <v/>
       </c>
       <c r="AI3" s="17">
-        <f>P3</f>
+        <f>AH3</f>
         <v/>
       </c>
       <c r="AJ3" s="17">
-        <f>P3</f>
+        <f>AI3</f>
         <v/>
       </c>
       <c r="AK3" s="17">
-        <f>P3</f>
+        <f>AJ3</f>
         <v/>
       </c>
       <c r="AL3" s="17">
-        <f>P3</f>
+        <f>AK3</f>
         <v/>
       </c>
     </row>
@@ -8015,87 +8015,87 @@
         <v/>
       </c>
       <c r="R4" s="17">
-        <f>P4</f>
+        <f>Q4</f>
         <v/>
       </c>
       <c r="S4" s="17">
-        <f>P4</f>
+        <f>R4</f>
         <v/>
       </c>
       <c r="T4" s="17">
-        <f>P4</f>
+        <f>S4</f>
         <v/>
       </c>
       <c r="U4" s="17">
-        <f>P4</f>
+        <f>T4</f>
         <v/>
       </c>
       <c r="V4" s="17">
-        <f>P4</f>
+        <f>U4</f>
         <v/>
       </c>
       <c r="W4" s="17">
-        <f>P4</f>
+        <f>V4</f>
         <v/>
       </c>
       <c r="X4" s="17">
-        <f>P4</f>
+        <f>W4</f>
         <v/>
       </c>
       <c r="Y4" s="17">
-        <f>P4</f>
+        <f>X4</f>
         <v/>
       </c>
       <c r="Z4" s="17">
-        <f>P4</f>
+        <f>Y4</f>
         <v/>
       </c>
       <c r="AA4" s="17">
-        <f>P4</f>
+        <f>Z4</f>
         <v/>
       </c>
       <c r="AB4" s="17">
-        <f>P4</f>
+        <f>AA4</f>
         <v/>
       </c>
       <c r="AC4" s="17">
-        <f>P4</f>
+        <f>AB4</f>
         <v/>
       </c>
       <c r="AD4" s="17">
-        <f>P4</f>
+        <f>AC4</f>
         <v/>
       </c>
       <c r="AE4" s="17">
-        <f>P4</f>
+        <f>AD4</f>
         <v/>
       </c>
       <c r="AF4" s="17">
-        <f>P4</f>
+        <f>AE4</f>
         <v/>
       </c>
       <c r="AG4" s="17">
-        <f>P4</f>
+        <f>AF4</f>
         <v/>
       </c>
       <c r="AH4" s="17">
-        <f>P4</f>
+        <f>AG4</f>
         <v/>
       </c>
       <c r="AI4" s="17">
-        <f>P4</f>
+        <f>AH4</f>
         <v/>
       </c>
       <c r="AJ4" s="17">
-        <f>P4</f>
+        <f>AI4</f>
         <v/>
       </c>
       <c r="AK4" s="17">
-        <f>P4</f>
+        <f>AJ4</f>
         <v/>
       </c>
       <c r="AL4" s="17">
-        <f>P4</f>
+        <f>AK4</f>
         <v/>
       </c>
     </row>
@@ -8170,87 +8170,87 @@
         <v/>
       </c>
       <c r="R5" s="14">
-        <f>P5</f>
+        <f>Q5</f>
         <v/>
       </c>
       <c r="S5" s="14">
-        <f>P5</f>
+        <f>R5</f>
         <v/>
       </c>
       <c r="T5" s="14">
-        <f>P5</f>
+        <f>S5</f>
         <v/>
       </c>
       <c r="U5" s="14">
-        <f>P5</f>
+        <f>T5</f>
         <v/>
       </c>
       <c r="V5" s="14">
-        <f>P5</f>
+        <f>U5</f>
         <v/>
       </c>
       <c r="W5" s="14">
-        <f>P5</f>
+        <f>V5</f>
         <v/>
       </c>
       <c r="X5" s="14">
-        <f>P5</f>
+        <f>W5</f>
         <v/>
       </c>
       <c r="Y5" s="14">
-        <f>P5</f>
+        <f>X5</f>
         <v/>
       </c>
       <c r="Z5" s="14">
-        <f>P5</f>
+        <f>Y5</f>
         <v/>
       </c>
       <c r="AA5" s="14">
-        <f>P5</f>
+        <f>Z5</f>
         <v/>
       </c>
       <c r="AB5" s="14">
-        <f>P5</f>
+        <f>AA5</f>
         <v/>
       </c>
       <c r="AC5" s="14">
-        <f>P5</f>
+        <f>AB5</f>
         <v/>
       </c>
       <c r="AD5" s="14">
-        <f>P5</f>
+        <f>AC5</f>
         <v/>
       </c>
       <c r="AE5" s="14">
-        <f>P5</f>
+        <f>AD5</f>
         <v/>
       </c>
       <c r="AF5" s="14">
-        <f>P5</f>
+        <f>AE5</f>
         <v/>
       </c>
       <c r="AG5" s="14">
-        <f>P5</f>
+        <f>AF5</f>
         <v/>
       </c>
       <c r="AH5" s="14">
-        <f>P5</f>
+        <f>AG5</f>
         <v/>
       </c>
       <c r="AI5" s="14">
-        <f>P5</f>
+        <f>AH5</f>
         <v/>
       </c>
       <c r="AJ5" s="14">
-        <f>P5</f>
+        <f>AI5</f>
         <v/>
       </c>
       <c r="AK5" s="14">
-        <f>P5</f>
+        <f>AJ5</f>
         <v/>
       </c>
       <c r="AL5" s="14">
-        <f>P5</f>
+        <f>AK5</f>
         <v/>
       </c>
     </row>
@@ -8480,87 +8480,87 @@
         <v/>
       </c>
       <c r="R7" s="15">
-        <f>P7</f>
+        <f>Q7</f>
         <v/>
       </c>
       <c r="S7" s="15">
-        <f>P7</f>
+        <f>R7</f>
         <v/>
       </c>
       <c r="T7" s="15">
-        <f>P7</f>
+        <f>S7</f>
         <v/>
       </c>
       <c r="U7" s="15">
-        <f>P7</f>
+        <f>T7</f>
         <v/>
       </c>
       <c r="V7" s="15">
-        <f>P7</f>
+        <f>U7</f>
         <v/>
       </c>
       <c r="W7" s="15">
-        <f>P7</f>
+        <f>V7</f>
         <v/>
       </c>
       <c r="X7" s="15">
-        <f>P7</f>
+        <f>W7</f>
         <v/>
       </c>
       <c r="Y7" s="15">
-        <f>P7</f>
+        <f>X7</f>
         <v/>
       </c>
       <c r="Z7" s="15">
-        <f>P7</f>
+        <f>Y7</f>
         <v/>
       </c>
       <c r="AA7" s="15">
-        <f>P7</f>
+        <f>Z7</f>
         <v/>
       </c>
       <c r="AB7" s="15">
-        <f>P7</f>
+        <f>AA7</f>
         <v/>
       </c>
       <c r="AC7" s="15">
-        <f>P7</f>
+        <f>AB7</f>
         <v/>
       </c>
       <c r="AD7" s="15">
-        <f>P7</f>
+        <f>AC7</f>
         <v/>
       </c>
       <c r="AE7" s="15">
-        <f>P7</f>
+        <f>AD7</f>
         <v/>
       </c>
       <c r="AF7" s="15">
-        <f>P7</f>
+        <f>AE7</f>
         <v/>
       </c>
       <c r="AG7" s="15">
-        <f>P7</f>
+        <f>AF7</f>
         <v/>
       </c>
       <c r="AH7" s="15">
-        <f>P7</f>
+        <f>AG7</f>
         <v/>
       </c>
       <c r="AI7" s="15">
-        <f>P7</f>
+        <f>AH7</f>
         <v/>
       </c>
       <c r="AJ7" s="15">
-        <f>P7</f>
+        <f>AI7</f>
         <v/>
       </c>
       <c r="AK7" s="15">
-        <f>P7</f>
+        <f>AJ7</f>
         <v/>
       </c>
       <c r="AL7" s="15">
-        <f>P7</f>
+        <f>AK7</f>
         <v/>
       </c>
     </row>
@@ -8635,87 +8635,87 @@
         <v/>
       </c>
       <c r="R8" s="15">
-        <f>P8</f>
+        <f>Q8</f>
         <v/>
       </c>
       <c r="S8" s="15">
-        <f>P8</f>
+        <f>R8</f>
         <v/>
       </c>
       <c r="T8" s="15">
-        <f>P8</f>
+        <f>S8</f>
         <v/>
       </c>
       <c r="U8" s="15">
-        <f>P8</f>
+        <f>T8</f>
         <v/>
       </c>
       <c r="V8" s="15">
-        <f>P8</f>
+        <f>U8</f>
         <v/>
       </c>
       <c r="W8" s="15">
-        <f>P8</f>
+        <f>V8</f>
         <v/>
       </c>
       <c r="X8" s="15">
-        <f>P8</f>
+        <f>W8</f>
         <v/>
       </c>
       <c r="Y8" s="15">
-        <f>P8</f>
+        <f>X8</f>
         <v/>
       </c>
       <c r="Z8" s="15">
-        <f>P8</f>
+        <f>Y8</f>
         <v/>
       </c>
       <c r="AA8" s="15">
-        <f>P8</f>
+        <f>Z8</f>
         <v/>
       </c>
       <c r="AB8" s="15">
-        <f>P8</f>
+        <f>AA8</f>
         <v/>
       </c>
       <c r="AC8" s="15">
-        <f>P8</f>
+        <f>AB8</f>
         <v/>
       </c>
       <c r="AD8" s="15">
-        <f>P8</f>
+        <f>AC8</f>
         <v/>
       </c>
       <c r="AE8" s="15">
-        <f>P8</f>
+        <f>AD8</f>
         <v/>
       </c>
       <c r="AF8" s="15">
-        <f>P8</f>
+        <f>AE8</f>
         <v/>
       </c>
       <c r="AG8" s="15">
-        <f>P8</f>
+        <f>AF8</f>
         <v/>
       </c>
       <c r="AH8" s="15">
-        <f>P8</f>
+        <f>AG8</f>
         <v/>
       </c>
       <c r="AI8" s="15">
-        <f>P8</f>
+        <f>AH8</f>
         <v/>
       </c>
       <c r="AJ8" s="15">
-        <f>P8</f>
+        <f>AI8</f>
         <v/>
       </c>
       <c r="AK8" s="15">
-        <f>P8</f>
+        <f>AJ8</f>
         <v/>
       </c>
       <c r="AL8" s="15">
-        <f>P8</f>
+        <f>AK8</f>
         <v/>
       </c>
     </row>
@@ -8790,87 +8790,87 @@
         <v/>
       </c>
       <c r="R9" s="14">
-        <f>P9</f>
+        <f>Q9</f>
         <v/>
       </c>
       <c r="S9" s="14">
-        <f>P9</f>
+        <f>R9</f>
         <v/>
       </c>
       <c r="T9" s="14">
-        <f>P9</f>
+        <f>S9</f>
         <v/>
       </c>
       <c r="U9" s="14">
-        <f>P9</f>
+        <f>T9</f>
         <v/>
       </c>
       <c r="V9" s="14">
-        <f>P9</f>
+        <f>U9</f>
         <v/>
       </c>
       <c r="W9" s="14">
-        <f>P9</f>
+        <f>V9</f>
         <v/>
       </c>
       <c r="X9" s="14">
-        <f>P9</f>
+        <f>W9</f>
         <v/>
       </c>
       <c r="Y9" s="14">
-        <f>P9</f>
+        <f>X9</f>
         <v/>
       </c>
       <c r="Z9" s="14">
-        <f>P9</f>
+        <f>Y9</f>
         <v/>
       </c>
       <c r="AA9" s="14">
-        <f>P9</f>
+        <f>Z9</f>
         <v/>
       </c>
       <c r="AB9" s="14">
-        <f>P9</f>
+        <f>AA9</f>
         <v/>
       </c>
       <c r="AC9" s="14">
-        <f>P9</f>
+        <f>AB9</f>
         <v/>
       </c>
       <c r="AD9" s="14">
-        <f>P9</f>
+        <f>AC9</f>
         <v/>
       </c>
       <c r="AE9" s="14">
-        <f>P9</f>
+        <f>AD9</f>
         <v/>
       </c>
       <c r="AF9" s="14">
-        <f>P9</f>
+        <f>AE9</f>
         <v/>
       </c>
       <c r="AG9" s="14">
-        <f>P9</f>
+        <f>AF9</f>
         <v/>
       </c>
       <c r="AH9" s="14">
-        <f>P9</f>
+        <f>AG9</f>
         <v/>
       </c>
       <c r="AI9" s="14">
-        <f>P9</f>
+        <f>AH9</f>
         <v/>
       </c>
       <c r="AJ9" s="14">
-        <f>P9</f>
+        <f>AI9</f>
         <v/>
       </c>
       <c r="AK9" s="14">
-        <f>P9</f>
+        <f>AJ9</f>
         <v/>
       </c>
       <c r="AL9" s="14">
-        <f>P9</f>
+        <f>AK9</f>
         <v/>
       </c>
     </row>
@@ -8945,87 +8945,87 @@
         <v/>
       </c>
       <c r="R10" s="17">
-        <f>P10</f>
+        <f>Q10</f>
         <v/>
       </c>
       <c r="S10" s="17">
-        <f>P10</f>
+        <f>R10</f>
         <v/>
       </c>
       <c r="T10" s="17">
-        <f>P10</f>
+        <f>S10</f>
         <v/>
       </c>
       <c r="U10" s="17">
-        <f>P10</f>
+        <f>T10</f>
         <v/>
       </c>
       <c r="V10" s="17">
-        <f>P10</f>
+        <f>U10</f>
         <v/>
       </c>
       <c r="W10" s="17">
-        <f>P10</f>
+        <f>V10</f>
         <v/>
       </c>
       <c r="X10" s="17">
-        <f>P10</f>
+        <f>W10</f>
         <v/>
       </c>
       <c r="Y10" s="17">
-        <f>P10</f>
+        <f>X10</f>
         <v/>
       </c>
       <c r="Z10" s="17">
-        <f>P10</f>
+        <f>Y10</f>
         <v/>
       </c>
       <c r="AA10" s="17">
-        <f>P10</f>
+        <f>Z10</f>
         <v/>
       </c>
       <c r="AB10" s="17">
-        <f>P10</f>
+        <f>AA10</f>
         <v/>
       </c>
       <c r="AC10" s="17">
-        <f>P10</f>
+        <f>AB10</f>
         <v/>
       </c>
       <c r="AD10" s="17">
-        <f>P10</f>
+        <f>AC10</f>
         <v/>
       </c>
       <c r="AE10" s="17">
-        <f>P10</f>
+        <f>AD10</f>
         <v/>
       </c>
       <c r="AF10" s="17">
-        <f>P10</f>
+        <f>AE10</f>
         <v/>
       </c>
       <c r="AG10" s="17">
-        <f>P10</f>
+        <f>AF10</f>
         <v/>
       </c>
       <c r="AH10" s="17">
-        <f>P10</f>
+        <f>AG10</f>
         <v/>
       </c>
       <c r="AI10" s="17">
-        <f>P10</f>
+        <f>AH10</f>
         <v/>
       </c>
       <c r="AJ10" s="17">
-        <f>P10</f>
+        <f>AI10</f>
         <v/>
       </c>
       <c r="AK10" s="17">
-        <f>P10</f>
+        <f>AJ10</f>
         <v/>
       </c>
       <c r="AL10" s="17">
-        <f>P10</f>
+        <f>AK10</f>
         <v/>
       </c>
     </row>
@@ -9100,87 +9100,87 @@
         <v/>
       </c>
       <c r="R11" s="14">
-        <f>P11</f>
+        <f>Q11</f>
         <v/>
       </c>
       <c r="S11" s="14">
-        <f>P11</f>
+        <f>R11</f>
         <v/>
       </c>
       <c r="T11" s="14">
-        <f>P11</f>
+        <f>S11</f>
         <v/>
       </c>
       <c r="U11" s="14">
-        <f>P11</f>
+        <f>T11</f>
         <v/>
       </c>
       <c r="V11" s="14">
-        <f>P11</f>
+        <f>U11</f>
         <v/>
       </c>
       <c r="W11" s="14">
-        <f>P11</f>
+        <f>V11</f>
         <v/>
       </c>
       <c r="X11" s="14">
-        <f>P11</f>
+        <f>W11</f>
         <v/>
       </c>
       <c r="Y11" s="14">
-        <f>P11</f>
+        <f>X11</f>
         <v/>
       </c>
       <c r="Z11" s="14">
-        <f>P11</f>
+        <f>Y11</f>
         <v/>
       </c>
       <c r="AA11" s="14">
-        <f>P11</f>
+        <f>Z11</f>
         <v/>
       </c>
       <c r="AB11" s="14">
-        <f>P11</f>
+        <f>AA11</f>
         <v/>
       </c>
       <c r="AC11" s="14">
-        <f>P11</f>
+        <f>AB11</f>
         <v/>
       </c>
       <c r="AD11" s="14">
-        <f>P11</f>
+        <f>AC11</f>
         <v/>
       </c>
       <c r="AE11" s="14">
-        <f>P11</f>
+        <f>AD11</f>
         <v/>
       </c>
       <c r="AF11" s="14">
-        <f>P11</f>
+        <f>AE11</f>
         <v/>
       </c>
       <c r="AG11" s="14">
-        <f>P11</f>
+        <f>AF11</f>
         <v/>
       </c>
       <c r="AH11" s="14">
-        <f>P11</f>
+        <f>AG11</f>
         <v/>
       </c>
       <c r="AI11" s="14">
-        <f>P11</f>
+        <f>AH11</f>
         <v/>
       </c>
       <c r="AJ11" s="14">
-        <f>P11</f>
+        <f>AI11</f>
         <v/>
       </c>
       <c r="AK11" s="14">
-        <f>P11</f>
+        <f>AJ11</f>
         <v/>
       </c>
       <c r="AL11" s="14">
-        <f>P11</f>
+        <f>AK11</f>
         <v/>
       </c>
     </row>
@@ -9255,87 +9255,87 @@
         <v/>
       </c>
       <c r="R12" s="15">
-        <f>P12</f>
+        <f>Q12</f>
         <v/>
       </c>
       <c r="S12" s="15">
-        <f>P12</f>
+        <f>R12</f>
         <v/>
       </c>
       <c r="T12" s="15">
-        <f>P12</f>
+        <f>S12</f>
         <v/>
       </c>
       <c r="U12" s="15">
-        <f>P12</f>
+        <f>T12</f>
         <v/>
       </c>
       <c r="V12" s="15">
-        <f>P12</f>
+        <f>U12</f>
         <v/>
       </c>
       <c r="W12" s="15">
-        <f>P12</f>
+        <f>V12</f>
         <v/>
       </c>
       <c r="X12" s="15">
-        <f>P12</f>
+        <f>W12</f>
         <v/>
       </c>
       <c r="Y12" s="15">
-        <f>P12</f>
+        <f>X12</f>
         <v/>
       </c>
       <c r="Z12" s="15">
-        <f>P12</f>
+        <f>Y12</f>
         <v/>
       </c>
       <c r="AA12" s="15">
-        <f>P12</f>
+        <f>Z12</f>
         <v/>
       </c>
       <c r="AB12" s="15">
-        <f>P12</f>
+        <f>AA12</f>
         <v/>
       </c>
       <c r="AC12" s="15">
-        <f>P12</f>
+        <f>AB12</f>
         <v/>
       </c>
       <c r="AD12" s="15">
-        <f>P12</f>
+        <f>AC12</f>
         <v/>
       </c>
       <c r="AE12" s="15">
-        <f>P12</f>
+        <f>AD12</f>
         <v/>
       </c>
       <c r="AF12" s="15">
-        <f>P12</f>
+        <f>AE12</f>
         <v/>
       </c>
       <c r="AG12" s="15">
-        <f>P12</f>
+        <f>AF12</f>
         <v/>
       </c>
       <c r="AH12" s="15">
-        <f>P12</f>
+        <f>AG12</f>
         <v/>
       </c>
       <c r="AI12" s="15">
-        <f>P12</f>
+        <f>AH12</f>
         <v/>
       </c>
       <c r="AJ12" s="15">
-        <f>P12</f>
+        <f>AI12</f>
         <v/>
       </c>
       <c r="AK12" s="15">
-        <f>P12</f>
+        <f>AJ12</f>
         <v/>
       </c>
       <c r="AL12" s="15">
-        <f>P12</f>
+        <f>AK12</f>
         <v/>
       </c>
     </row>
@@ -9410,87 +9410,87 @@
         <v/>
       </c>
       <c r="R13" s="15">
-        <f>P13</f>
+        <f>Q13</f>
         <v/>
       </c>
       <c r="S13" s="15">
-        <f>P13</f>
+        <f>R13</f>
         <v/>
       </c>
       <c r="T13" s="15">
-        <f>P13</f>
+        <f>S13</f>
         <v/>
       </c>
       <c r="U13" s="15">
-        <f>P13</f>
+        <f>T13</f>
         <v/>
       </c>
       <c r="V13" s="15">
-        <f>P13</f>
+        <f>U13</f>
         <v/>
       </c>
       <c r="W13" s="15">
-        <f>P13</f>
+        <f>V13</f>
         <v/>
       </c>
       <c r="X13" s="15">
-        <f>P13</f>
+        <f>W13</f>
         <v/>
       </c>
       <c r="Y13" s="15">
-        <f>P13</f>
+        <f>X13</f>
         <v/>
       </c>
       <c r="Z13" s="15">
-        <f>P13</f>
+        <f>Y13</f>
         <v/>
       </c>
       <c r="AA13" s="15">
-        <f>P13</f>
+        <f>Z13</f>
         <v/>
       </c>
       <c r="AB13" s="15">
-        <f>P13</f>
+        <f>AA13</f>
         <v/>
       </c>
       <c r="AC13" s="15">
-        <f>P13</f>
+        <f>AB13</f>
         <v/>
       </c>
       <c r="AD13" s="15">
-        <f>P13</f>
+        <f>AC13</f>
         <v/>
       </c>
       <c r="AE13" s="15">
-        <f>P13</f>
+        <f>AD13</f>
         <v/>
       </c>
       <c r="AF13" s="15">
-        <f>P13</f>
+        <f>AE13</f>
         <v/>
       </c>
       <c r="AG13" s="15">
-        <f>P13</f>
+        <f>AF13</f>
         <v/>
       </c>
       <c r="AH13" s="15">
-        <f>P13</f>
+        <f>AG13</f>
         <v/>
       </c>
       <c r="AI13" s="15">
-        <f>P13</f>
+        <f>AH13</f>
         <v/>
       </c>
       <c r="AJ13" s="15">
-        <f>P13</f>
+        <f>AI13</f>
         <v/>
       </c>
       <c r="AK13" s="15">
-        <f>P13</f>
+        <f>AJ13</f>
         <v/>
       </c>
       <c r="AL13" s="15">
-        <f>P13</f>
+        <f>AK13</f>
         <v/>
       </c>
     </row>
@@ -9565,87 +9565,87 @@
         <v/>
       </c>
       <c r="R14" s="15">
-        <f>P14</f>
+        <f>Q14</f>
         <v/>
       </c>
       <c r="S14" s="15">
-        <f>P14</f>
+        <f>R14</f>
         <v/>
       </c>
       <c r="T14" s="15">
-        <f>P14</f>
+        <f>S14</f>
         <v/>
       </c>
       <c r="U14" s="15">
-        <f>P14</f>
+        <f>T14</f>
         <v/>
       </c>
       <c r="V14" s="15">
-        <f>P14</f>
+        <f>U14</f>
         <v/>
       </c>
       <c r="W14" s="15">
-        <f>P14</f>
+        <f>V14</f>
         <v/>
       </c>
       <c r="X14" s="15">
-        <f>P14</f>
+        <f>W14</f>
         <v/>
       </c>
       <c r="Y14" s="15">
-        <f>P14</f>
+        <f>X14</f>
         <v/>
       </c>
       <c r="Z14" s="15">
-        <f>P14</f>
+        <f>Y14</f>
         <v/>
       </c>
       <c r="AA14" s="15">
-        <f>P14</f>
+        <f>Z14</f>
         <v/>
       </c>
       <c r="AB14" s="15">
-        <f>P14</f>
+        <f>AA14</f>
         <v/>
       </c>
       <c r="AC14" s="15">
-        <f>P14</f>
+        <f>AB14</f>
         <v/>
       </c>
       <c r="AD14" s="15">
-        <f>P14</f>
+        <f>AC14</f>
         <v/>
       </c>
       <c r="AE14" s="15">
-        <f>P14</f>
+        <f>AD14</f>
         <v/>
       </c>
       <c r="AF14" s="15">
-        <f>P14</f>
+        <f>AE14</f>
         <v/>
       </c>
       <c r="AG14" s="15">
-        <f>P14</f>
+        <f>AF14</f>
         <v/>
       </c>
       <c r="AH14" s="15">
-        <f>P14</f>
+        <f>AG14</f>
         <v/>
       </c>
       <c r="AI14" s="15">
-        <f>P14</f>
+        <f>AH14</f>
         <v/>
       </c>
       <c r="AJ14" s="15">
-        <f>P14</f>
+        <f>AI14</f>
         <v/>
       </c>
       <c r="AK14" s="15">
-        <f>P14</f>
+        <f>AJ14</f>
         <v/>
       </c>
       <c r="AL14" s="15">
-        <f>P14</f>
+        <f>AK14</f>
         <v/>
       </c>
     </row>
@@ -9720,87 +9720,87 @@
         <v/>
       </c>
       <c r="R15" s="14">
-        <f>P15</f>
+        <f>Q15</f>
         <v/>
       </c>
       <c r="S15" s="14">
-        <f>P15</f>
+        <f>R15</f>
         <v/>
       </c>
       <c r="T15" s="14">
-        <f>P15</f>
+        <f>S15</f>
         <v/>
       </c>
       <c r="U15" s="14">
-        <f>P15</f>
+        <f>T15</f>
         <v/>
       </c>
       <c r="V15" s="14">
-        <f>P15</f>
+        <f>U15</f>
         <v/>
       </c>
       <c r="W15" s="14">
-        <f>P15</f>
+        <f>V15</f>
         <v/>
       </c>
       <c r="X15" s="14">
-        <f>P15</f>
+        <f>W15</f>
         <v/>
       </c>
       <c r="Y15" s="14">
-        <f>P15</f>
+        <f>X15</f>
         <v/>
       </c>
       <c r="Z15" s="14">
-        <f>P15</f>
+        <f>Y15</f>
         <v/>
       </c>
       <c r="AA15" s="14">
-        <f>P15</f>
+        <f>Z15</f>
         <v/>
       </c>
       <c r="AB15" s="14">
-        <f>P15</f>
+        <f>AA15</f>
         <v/>
       </c>
       <c r="AC15" s="14">
-        <f>P15</f>
+        <f>AB15</f>
         <v/>
       </c>
       <c r="AD15" s="14">
-        <f>P15</f>
+        <f>AC15</f>
         <v/>
       </c>
       <c r="AE15" s="14">
-        <f>P15</f>
+        <f>AD15</f>
         <v/>
       </c>
       <c r="AF15" s="14">
-        <f>P15</f>
+        <f>AE15</f>
         <v/>
       </c>
       <c r="AG15" s="14">
-        <f>P15</f>
+        <f>AF15</f>
         <v/>
       </c>
       <c r="AH15" s="14">
-        <f>P15</f>
+        <f>AG15</f>
         <v/>
       </c>
       <c r="AI15" s="14">
-        <f>P15</f>
+        <f>AH15</f>
         <v/>
       </c>
       <c r="AJ15" s="14">
-        <f>P15</f>
+        <f>AI15</f>
         <v/>
       </c>
       <c r="AK15" s="14">
-        <f>P15</f>
+        <f>AJ15</f>
         <v/>
       </c>
       <c r="AL15" s="14">
-        <f>P15</f>
+        <f>AK15</f>
         <v/>
       </c>
     </row>
@@ -9875,87 +9875,87 @@
         <v/>
       </c>
       <c r="R16" s="15">
-        <f>P16</f>
+        <f>Q16</f>
         <v/>
       </c>
       <c r="S16" s="15">
-        <f>P16</f>
+        <f>R16</f>
         <v/>
       </c>
       <c r="T16" s="15">
-        <f>P16</f>
+        <f>S16</f>
         <v/>
       </c>
       <c r="U16" s="15">
-        <f>P16</f>
+        <f>T16</f>
         <v/>
       </c>
       <c r="V16" s="15">
-        <f>P16</f>
+        <f>U16</f>
         <v/>
       </c>
       <c r="W16" s="15">
-        <f>P16</f>
+        <f>V16</f>
         <v/>
       </c>
       <c r="X16" s="15">
-        <f>P16</f>
+        <f>W16</f>
         <v/>
       </c>
       <c r="Y16" s="15">
-        <f>P16</f>
+        <f>X16</f>
         <v/>
       </c>
       <c r="Z16" s="15">
-        <f>P16</f>
+        <f>Y16</f>
         <v/>
       </c>
       <c r="AA16" s="15">
-        <f>P16</f>
+        <f>Z16</f>
         <v/>
       </c>
       <c r="AB16" s="15">
-        <f>P16</f>
+        <f>AA16</f>
         <v/>
       </c>
       <c r="AC16" s="15">
-        <f>P16</f>
+        <f>AB16</f>
         <v/>
       </c>
       <c r="AD16" s="15">
-        <f>P16</f>
+        <f>AC16</f>
         <v/>
       </c>
       <c r="AE16" s="15">
-        <f>P16</f>
+        <f>AD16</f>
         <v/>
       </c>
       <c r="AF16" s="15">
-        <f>P16</f>
+        <f>AE16</f>
         <v/>
       </c>
       <c r="AG16" s="15">
-        <f>P16</f>
+        <f>AF16</f>
         <v/>
       </c>
       <c r="AH16" s="15">
-        <f>P16</f>
+        <f>AG16</f>
         <v/>
       </c>
       <c r="AI16" s="15">
-        <f>P16</f>
+        <f>AH16</f>
         <v/>
       </c>
       <c r="AJ16" s="15">
-        <f>P16</f>
+        <f>AI16</f>
         <v/>
       </c>
       <c r="AK16" s="15">
-        <f>P16</f>
+        <f>AJ16</f>
         <v/>
       </c>
       <c r="AL16" s="15">
-        <f>P16</f>
+        <f>AK16</f>
         <v/>
       </c>
     </row>
@@ -10030,87 +10030,87 @@
         <v/>
       </c>
       <c r="R17" s="15">
-        <f>P17</f>
+        <f>Q17</f>
         <v/>
       </c>
       <c r="S17" s="15">
-        <f>P17</f>
+        <f>R17</f>
         <v/>
       </c>
       <c r="T17" s="15">
-        <f>P17</f>
+        <f>S17</f>
         <v/>
       </c>
       <c r="U17" s="15">
-        <f>P17</f>
+        <f>T17</f>
         <v/>
       </c>
       <c r="V17" s="15">
-        <f>P17</f>
+        <f>U17</f>
         <v/>
       </c>
       <c r="W17" s="15">
-        <f>P17</f>
+        <f>V17</f>
         <v/>
       </c>
       <c r="X17" s="15">
-        <f>P17</f>
+        <f>W17</f>
         <v/>
       </c>
       <c r="Y17" s="15">
-        <f>P17</f>
+        <f>X17</f>
         <v/>
       </c>
       <c r="Z17" s="15">
-        <f>P17</f>
+        <f>Y17</f>
         <v/>
       </c>
       <c r="AA17" s="15">
-        <f>P17</f>
+        <f>Z17</f>
         <v/>
       </c>
       <c r="AB17" s="15">
-        <f>P17</f>
+        <f>AA17</f>
         <v/>
       </c>
       <c r="AC17" s="15">
-        <f>P17</f>
+        <f>AB17</f>
         <v/>
       </c>
       <c r="AD17" s="15">
-        <f>P17</f>
+        <f>AC17</f>
         <v/>
       </c>
       <c r="AE17" s="15">
-        <f>P17</f>
+        <f>AD17</f>
         <v/>
       </c>
       <c r="AF17" s="15">
-        <f>P17</f>
+        <f>AE17</f>
         <v/>
       </c>
       <c r="AG17" s="15">
-        <f>P17</f>
+        <f>AF17</f>
         <v/>
       </c>
       <c r="AH17" s="15">
-        <f>P17</f>
+        <f>AG17</f>
         <v/>
       </c>
       <c r="AI17" s="15">
-        <f>P17</f>
+        <f>AH17</f>
         <v/>
       </c>
       <c r="AJ17" s="15">
-        <f>P17</f>
+        <f>AI17</f>
         <v/>
       </c>
       <c r="AK17" s="15">
-        <f>P17</f>
+        <f>AJ17</f>
         <v/>
       </c>
       <c r="AL17" s="15">
-        <f>P17</f>
+        <f>AK17</f>
         <v/>
       </c>
     </row>
@@ -10628,87 +10628,87 @@
         <v/>
       </c>
       <c r="R21" s="15">
-        <f>P21</f>
+        <f>Q21</f>
         <v/>
       </c>
       <c r="S21" s="15">
-        <f>P21</f>
+        <f>R21</f>
         <v/>
       </c>
       <c r="T21" s="15">
-        <f>P21</f>
+        <f>S21</f>
         <v/>
       </c>
       <c r="U21" s="15">
-        <f>P21</f>
+        <f>T21</f>
         <v/>
       </c>
       <c r="V21" s="15">
-        <f>P21</f>
+        <f>U21</f>
         <v/>
       </c>
       <c r="W21" s="15">
-        <f>P21</f>
+        <f>V21</f>
         <v/>
       </c>
       <c r="X21" s="15">
-        <f>P21</f>
+        <f>W21</f>
         <v/>
       </c>
       <c r="Y21" s="15">
-        <f>P21</f>
+        <f>X21</f>
         <v/>
       </c>
       <c r="Z21" s="15">
-        <f>P21</f>
+        <f>Y21</f>
         <v/>
       </c>
       <c r="AA21" s="15">
-        <f>P21</f>
+        <f>Z21</f>
         <v/>
       </c>
       <c r="AB21" s="15">
-        <f>P21</f>
+        <f>AA21</f>
         <v/>
       </c>
       <c r="AC21" s="15">
-        <f>P21</f>
+        <f>AB21</f>
         <v/>
       </c>
       <c r="AD21" s="15">
-        <f>P21</f>
+        <f>AC21</f>
         <v/>
       </c>
       <c r="AE21" s="15">
-        <f>P21</f>
+        <f>AD21</f>
         <v/>
       </c>
       <c r="AF21" s="15">
-        <f>P21</f>
+        <f>AE21</f>
         <v/>
       </c>
       <c r="AG21" s="15">
-        <f>P21</f>
+        <f>AF21</f>
         <v/>
       </c>
       <c r="AH21" s="15">
-        <f>P21</f>
+        <f>AG21</f>
         <v/>
       </c>
       <c r="AI21" s="15">
-        <f>P21</f>
+        <f>AH21</f>
         <v/>
       </c>
       <c r="AJ21" s="15">
-        <f>P21</f>
+        <f>AI21</f>
         <v/>
       </c>
       <c r="AK21" s="15">
-        <f>P21</f>
+        <f>AJ21</f>
         <v/>
       </c>
       <c r="AL21" s="15">
-        <f>P21</f>
+        <f>AK21</f>
         <v/>
       </c>
     </row>
@@ -10938,87 +10938,87 @@
         <v/>
       </c>
       <c r="R23" s="15">
-        <f>P23</f>
+        <f>Q23</f>
         <v/>
       </c>
       <c r="S23" s="15">
-        <f>P23</f>
+        <f>R23</f>
         <v/>
       </c>
       <c r="T23" s="15">
-        <f>P23</f>
+        <f>S23</f>
         <v/>
       </c>
       <c r="U23" s="15">
-        <f>P23</f>
+        <f>T23</f>
         <v/>
       </c>
       <c r="V23" s="15">
-        <f>P23</f>
+        <f>U23</f>
         <v/>
       </c>
       <c r="W23" s="15">
-        <f>P23</f>
+        <f>V23</f>
         <v/>
       </c>
       <c r="X23" s="15">
-        <f>P23</f>
+        <f>W23</f>
         <v/>
       </c>
       <c r="Y23" s="15">
-        <f>P23</f>
+        <f>X23</f>
         <v/>
       </c>
       <c r="Z23" s="15">
-        <f>P23</f>
+        <f>Y23</f>
         <v/>
       </c>
       <c r="AA23" s="15">
-        <f>P23</f>
+        <f>Z23</f>
         <v/>
       </c>
       <c r="AB23" s="15">
-        <f>P23</f>
+        <f>AA23</f>
         <v/>
       </c>
       <c r="AC23" s="15">
-        <f>P23</f>
+        <f>AB23</f>
         <v/>
       </c>
       <c r="AD23" s="15">
-        <f>P23</f>
+        <f>AC23</f>
         <v/>
       </c>
       <c r="AE23" s="15">
-        <f>P23</f>
+        <f>AD23</f>
         <v/>
       </c>
       <c r="AF23" s="15">
-        <f>P23</f>
+        <f>AE23</f>
         <v/>
       </c>
       <c r="AG23" s="15">
-        <f>P23</f>
+        <f>AF23</f>
         <v/>
       </c>
       <c r="AH23" s="15">
-        <f>P23</f>
+        <f>AG23</f>
         <v/>
       </c>
       <c r="AI23" s="15">
-        <f>P23</f>
+        <f>AH23</f>
         <v/>
       </c>
       <c r="AJ23" s="15">
-        <f>P23</f>
+        <f>AI23</f>
         <v/>
       </c>
       <c r="AK23" s="15">
-        <f>P23</f>
+        <f>AJ23</f>
         <v/>
       </c>
       <c r="AL23" s="15">
-        <f>P23</f>
+        <f>AK23</f>
         <v/>
       </c>
     </row>
@@ -11536,87 +11536,87 @@
         <v/>
       </c>
       <c r="U3" s="14">
-        <f>S3</f>
+        <f>T3</f>
         <v/>
       </c>
       <c r="V3" s="14">
-        <f>S3</f>
+        <f>U3</f>
         <v/>
       </c>
       <c r="W3" s="14">
-        <f>S3</f>
+        <f>V3</f>
         <v/>
       </c>
       <c r="X3" s="14">
-        <f>S3</f>
+        <f>W3</f>
         <v/>
       </c>
       <c r="Y3" s="14">
-        <f>S3</f>
+        <f>X3</f>
         <v/>
       </c>
       <c r="Z3" s="14">
-        <f>S3</f>
+        <f>Y3</f>
         <v/>
       </c>
       <c r="AA3" s="14">
-        <f>S3</f>
+        <f>Z3</f>
         <v/>
       </c>
       <c r="AB3" s="14">
-        <f>S3</f>
+        <f>AA3</f>
         <v/>
       </c>
       <c r="AC3" s="14">
-        <f>S3</f>
+        <f>AB3</f>
         <v/>
       </c>
       <c r="AD3" s="14">
-        <f>S3</f>
+        <f>AC3</f>
         <v/>
       </c>
       <c r="AE3" s="14">
-        <f>S3</f>
+        <f>AD3</f>
         <v/>
       </c>
       <c r="AF3" s="14">
-        <f>S3</f>
+        <f>AE3</f>
         <v/>
       </c>
       <c r="AG3" s="14">
-        <f>S3</f>
+        <f>AF3</f>
         <v/>
       </c>
       <c r="AH3" s="14">
-        <f>S3</f>
+        <f>AG3</f>
         <v/>
       </c>
       <c r="AI3" s="14">
-        <f>S3</f>
+        <f>AH3</f>
         <v/>
       </c>
       <c r="AJ3" s="14">
-        <f>S3</f>
+        <f>AI3</f>
         <v/>
       </c>
       <c r="AK3" s="14">
-        <f>S3</f>
+        <f>AJ3</f>
         <v/>
       </c>
       <c r="AL3" s="14">
-        <f>S3</f>
+        <f>AK3</f>
         <v/>
       </c>
       <c r="AM3" s="14">
-        <f>S3</f>
+        <f>AL3</f>
         <v/>
       </c>
       <c r="AN3" s="14">
-        <f>S3</f>
+        <f>AM3</f>
         <v/>
       </c>
       <c r="AO3" s="14">
-        <f>S3</f>
+        <f>AN3</f>
         <v/>
       </c>
     </row>
@@ -11848,87 +11848,87 @@
         <v/>
       </c>
       <c r="U5" s="14">
-        <f>S5</f>
+        <f>T5</f>
         <v/>
       </c>
       <c r="V5" s="14">
-        <f>S5</f>
+        <f>U5</f>
         <v/>
       </c>
       <c r="W5" s="14">
-        <f>S5</f>
+        <f>V5</f>
         <v/>
       </c>
       <c r="X5" s="14">
-        <f>S5</f>
+        <f>W5</f>
         <v/>
       </c>
       <c r="Y5" s="14">
-        <f>S5</f>
+        <f>X5</f>
         <v/>
       </c>
       <c r="Z5" s="14">
-        <f>S5</f>
+        <f>Y5</f>
         <v/>
       </c>
       <c r="AA5" s="14">
-        <f>S5</f>
+        <f>Z5</f>
         <v/>
       </c>
       <c r="AB5" s="14">
-        <f>S5</f>
+        <f>AA5</f>
         <v/>
       </c>
       <c r="AC5" s="14">
-        <f>S5</f>
+        <f>AB5</f>
         <v/>
       </c>
       <c r="AD5" s="14">
-        <f>S5</f>
+        <f>AC5</f>
         <v/>
       </c>
       <c r="AE5" s="14">
-        <f>S5</f>
+        <f>AD5</f>
         <v/>
       </c>
       <c r="AF5" s="14">
-        <f>S5</f>
+        <f>AE5</f>
         <v/>
       </c>
       <c r="AG5" s="14">
-        <f>S5</f>
+        <f>AF5</f>
         <v/>
       </c>
       <c r="AH5" s="14">
-        <f>S5</f>
+        <f>AG5</f>
         <v/>
       </c>
       <c r="AI5" s="14">
-        <f>S5</f>
+        <f>AH5</f>
         <v/>
       </c>
       <c r="AJ5" s="14">
-        <f>S5</f>
+        <f>AI5</f>
         <v/>
       </c>
       <c r="AK5" s="14">
-        <f>S5</f>
+        <f>AJ5</f>
         <v/>
       </c>
       <c r="AL5" s="14">
-        <f>S5</f>
+        <f>AK5</f>
         <v/>
       </c>
       <c r="AM5" s="14">
-        <f>S5</f>
+        <f>AL5</f>
         <v/>
       </c>
       <c r="AN5" s="14">
-        <f>S5</f>
+        <f>AM5</f>
         <v/>
       </c>
       <c r="AO5" s="14">
-        <f>S5</f>
+        <f>AN5</f>
         <v/>
       </c>
     </row>
@@ -13263,87 +13263,87 @@
         <v/>
       </c>
       <c r="U14" s="14">
-        <f>S14</f>
+        <f>T14</f>
         <v/>
       </c>
       <c r="V14" s="14">
-        <f>S14</f>
+        <f>U14</f>
         <v/>
       </c>
       <c r="W14" s="14">
-        <f>S14</f>
+        <f>V14</f>
         <v/>
       </c>
       <c r="X14" s="14">
-        <f>S14</f>
+        <f>W14</f>
         <v/>
       </c>
       <c r="Y14" s="14">
-        <f>S14</f>
+        <f>X14</f>
         <v/>
       </c>
       <c r="Z14" s="14">
-        <f>S14</f>
+        <f>Y14</f>
         <v/>
       </c>
       <c r="AA14" s="14">
-        <f>S14</f>
+        <f>Z14</f>
         <v/>
       </c>
       <c r="AB14" s="14">
-        <f>S14</f>
+        <f>AA14</f>
         <v/>
       </c>
       <c r="AC14" s="14">
-        <f>S14</f>
+        <f>AB14</f>
         <v/>
       </c>
       <c r="AD14" s="14">
-        <f>S14</f>
+        <f>AC14</f>
         <v/>
       </c>
       <c r="AE14" s="14">
-        <f>S14</f>
+        <f>AD14</f>
         <v/>
       </c>
       <c r="AF14" s="14">
-        <f>S14</f>
+        <f>AE14</f>
         <v/>
       </c>
       <c r="AG14" s="14">
-        <f>S14</f>
+        <f>AF14</f>
         <v/>
       </c>
       <c r="AH14" s="14">
-        <f>S14</f>
+        <f>AG14</f>
         <v/>
       </c>
       <c r="AI14" s="14">
-        <f>S14</f>
+        <f>AH14</f>
         <v/>
       </c>
       <c r="AJ14" s="14">
-        <f>S14</f>
+        <f>AI14</f>
         <v/>
       </c>
       <c r="AK14" s="14">
-        <f>S14</f>
+        <f>AJ14</f>
         <v/>
       </c>
       <c r="AL14" s="14">
-        <f>S14</f>
+        <f>AK14</f>
         <v/>
       </c>
       <c r="AM14" s="14">
-        <f>S14</f>
+        <f>AL14</f>
         <v/>
       </c>
       <c r="AN14" s="14">
-        <f>S14</f>
+        <f>AM14</f>
         <v/>
       </c>
       <c r="AO14" s="14">
-        <f>S14</f>
+        <f>AN14</f>
         <v/>
       </c>
     </row>
@@ -14010,87 +14010,87 @@
         <v/>
       </c>
       <c r="U19" s="14">
-        <f>S19</f>
+        <f>T19</f>
         <v/>
       </c>
       <c r="V19" s="14">
-        <f>S19</f>
+        <f>U19</f>
         <v/>
       </c>
       <c r="W19" s="14">
-        <f>S19</f>
+        <f>V19</f>
         <v/>
       </c>
       <c r="X19" s="14">
-        <f>S19</f>
+        <f>W19</f>
         <v/>
       </c>
       <c r="Y19" s="14">
-        <f>S19</f>
+        <f>X19</f>
         <v/>
       </c>
       <c r="Z19" s="14">
-        <f>S19</f>
+        <f>Y19</f>
         <v/>
       </c>
       <c r="AA19" s="14">
-        <f>S19</f>
+        <f>Z19</f>
         <v/>
       </c>
       <c r="AB19" s="14">
-        <f>S19</f>
+        <f>AA19</f>
         <v/>
       </c>
       <c r="AC19" s="14">
-        <f>S19</f>
+        <f>AB19</f>
         <v/>
       </c>
       <c r="AD19" s="14">
-        <f>S19</f>
+        <f>AC19</f>
         <v/>
       </c>
       <c r="AE19" s="14">
-        <f>S19</f>
+        <f>AD19</f>
         <v/>
       </c>
       <c r="AF19" s="14">
-        <f>S19</f>
+        <f>AE19</f>
         <v/>
       </c>
       <c r="AG19" s="14">
-        <f>S19</f>
+        <f>AF19</f>
         <v/>
       </c>
       <c r="AH19" s="14">
-        <f>S19</f>
+        <f>AG19</f>
         <v/>
       </c>
       <c r="AI19" s="14">
-        <f>S19</f>
+        <f>AH19</f>
         <v/>
       </c>
       <c r="AJ19" s="14">
-        <f>S19</f>
+        <f>AI19</f>
         <v/>
       </c>
       <c r="AK19" s="14">
-        <f>S19</f>
+        <f>AJ19</f>
         <v/>
       </c>
       <c r="AL19" s="14">
-        <f>S19</f>
+        <f>AK19</f>
         <v/>
       </c>
       <c r="AM19" s="14">
-        <f>S19</f>
+        <f>AL19</f>
         <v/>
       </c>
       <c r="AN19" s="14">
-        <f>S19</f>
+        <f>AM19</f>
         <v/>
       </c>
       <c r="AO19" s="14">
-        <f>S19</f>
+        <f>AN19</f>
         <v/>
       </c>
     </row>
@@ -15192,87 +15192,87 @@
         <v/>
       </c>
       <c r="U27" s="15">
-        <f>S27</f>
+        <f>T27</f>
         <v/>
       </c>
       <c r="V27" s="15">
-        <f>S27</f>
+        <f>U27</f>
         <v/>
       </c>
       <c r="W27" s="15">
-        <f>S27</f>
+        <f>V27</f>
         <v/>
       </c>
       <c r="X27" s="15">
-        <f>S27</f>
+        <f>W27</f>
         <v/>
       </c>
       <c r="Y27" s="15">
-        <f>S27</f>
+        <f>X27</f>
         <v/>
       </c>
       <c r="Z27" s="15">
-        <f>S27</f>
+        <f>Y27</f>
         <v/>
       </c>
       <c r="AA27" s="15">
-        <f>S27</f>
+        <f>Z27</f>
         <v/>
       </c>
       <c r="AB27" s="15">
-        <f>S27</f>
+        <f>AA27</f>
         <v/>
       </c>
       <c r="AC27" s="15">
-        <f>S27</f>
+        <f>AB27</f>
         <v/>
       </c>
       <c r="AD27" s="15">
-        <f>S27</f>
+        <f>AC27</f>
         <v/>
       </c>
       <c r="AE27" s="15">
-        <f>S27</f>
+        <f>AD27</f>
         <v/>
       </c>
       <c r="AF27" s="15">
-        <f>S27</f>
+        <f>AE27</f>
         <v/>
       </c>
       <c r="AG27" s="15">
-        <f>S27</f>
+        <f>AF27</f>
         <v/>
       </c>
       <c r="AH27" s="15">
-        <f>S27</f>
+        <f>AG27</f>
         <v/>
       </c>
       <c r="AI27" s="15">
-        <f>S27</f>
+        <f>AH27</f>
         <v/>
       </c>
       <c r="AJ27" s="15">
-        <f>S27</f>
+        <f>AI27</f>
         <v/>
       </c>
       <c r="AK27" s="15">
-        <f>S27</f>
+        <f>AJ27</f>
         <v/>
       </c>
       <c r="AL27" s="15">
-        <f>S27</f>
+        <f>AK27</f>
         <v/>
       </c>
       <c r="AM27" s="15">
-        <f>S27</f>
+        <f>AL27</f>
         <v/>
       </c>
       <c r="AN27" s="15">
-        <f>S27</f>
+        <f>AM27</f>
         <v/>
       </c>
       <c r="AO27" s="15">
-        <f>S27</f>
+        <f>AN27</f>
         <v/>
       </c>
     </row>
